--- a/experiments/results/abp/iteration-bfs-reverse/abp-sat-iteration-bfs-reverse.xlsx
+++ b/experiments/results/abp/iteration-bfs-reverse/abp-sat-iteration-bfs-reverse.xlsx
@@ -11947,7 +11947,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>45000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -11973,28 +11973,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>870</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>871</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>904</v>
+        <v>870</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30024.3</t>
+          <t>31066.3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>82322</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>165074</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/experiments/results/abp/iteration-bfs-reverse/abp-sat-iteration-bfs-reverse.xlsx
+++ b/experiments/results/abp/iteration-bfs-reverse/abp-sat-iteration-bfs-reverse.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ite_abp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ite_abp_x0.5_has_hole" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ite_abp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ite_abp_x0.75_has_hole" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ite_abp_x1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ite_abp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ite_abp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_abp_x0.5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_abp_x0.5_no_hole" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_abp_x0.75" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_abp_x0.75_no_hole" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_abp_x1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_abp_x1.25" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ite_abp_x1.5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -423,72 +435,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -533,25 +545,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -612,12 +624,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -678,12 +690,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -744,7 +756,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -810,12 +822,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -876,12 +888,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -942,12 +954,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>87</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1008,12 +1020,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>305</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1074,12 +1086,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>115.8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>373752</t>
+          <t>360</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1127,25 +1139,25 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>156.2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1206,12 +1218,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>213.9</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4119</t>
+          <t>154</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1272,12 +1284,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>187.7</t>
+          <t>175.9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>419</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1330,20 +1342,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>189</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5977.1</t>
+          <t>5823.5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1812010</t>
+          <t>1813637</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1392,20 +1404,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>189</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6020.1</t>
+          <t>5834.5</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1812014</t>
+          <t>1813881</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1454,23 +1466,27 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>181</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5370.9</t>
+          <t>3136.1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1811929</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>16278</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1516,23 +1532,27 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>181</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>3701.1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1811873</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>22191</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1586,12 +1606,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3524.5</t>
+          <t>1302.2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>159786</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1652,12 +1672,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>7084.1</t>
+          <t>5897.4</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>149350</t>
+          <t>42580</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1705,25 +1725,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>259</v>
+        <v>130</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4982.6</t>
+          <t>1381.4</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>61413</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1771,25 +1791,25 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>168</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>7436.3</t>
+          <t>5577.9</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>343104</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1850,12 +1870,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6415.3</t>
+          <t>6290.1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>113047</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1903,25 +1923,25 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>165</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7248.8</t>
+          <t>2177.2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>60256</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1982,12 +2002,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8023</t>
+          <t>7291.3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>119115</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2040,23 +2060,27 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>291</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11314.1</t>
+          <t>9805.6</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1811767</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>78702</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2073,72 +2097,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -2183,25 +2207,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -2262,12 +2286,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2328,12 +2352,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2394,7 +2418,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2460,12 +2484,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2526,12 +2550,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2592,12 +2616,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>23.6</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2658,12 +2682,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>161</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2724,12 +2748,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>115.8</t>
+          <t>134.1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>373752</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2777,25 +2801,25 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>156.2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>12434</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2856,12 +2880,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>213.9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2922,12 +2946,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>175.9</t>
+          <t>187.7</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>654</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2980,20 +3004,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>192</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5823.5</t>
+          <t>5977.1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1813637</t>
+          <t>1812010</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -3042,20 +3066,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>192</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5834.5</t>
+          <t>6020.1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1813881</t>
+          <t>1812014</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -3104,27 +3128,23 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3136.1</t>
+          <t>5370.9</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16278</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811929</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3170,27 +3190,23 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>200</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3701.1</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>22191</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811873</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3244,12 +3260,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1302.2</t>
+          <t>3524.5</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>159786</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3310,12 +3326,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5897.4</t>
+          <t>7084.1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>42580</t>
+          <t>149350</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3363,25 +3379,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>260</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>130</v>
+        <v>259</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1381.4</t>
+          <t>4982.6</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>61413</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3429,25 +3445,25 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>223</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>224</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>168</v>
+        <v>223</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5577.9</t>
+          <t>7436.3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>343104</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3508,12 +3524,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>6290.1</t>
+          <t>6415.3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>113047</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3561,25 +3577,25 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>328</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>164</v>
+        <v>327</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2177.2</t>
+          <t>7248.8</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>60256</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3640,12 +3656,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7291.3</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>119115</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3698,27 +3714,23 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>298</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>9805.6</t>
+          <t>11314.1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>78702</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811767</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3735,72 +3747,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -3845,25 +3857,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>32</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -3924,12 +3936,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>36</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -3990,12 +4002,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -4056,12 +4068,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>73</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -4122,12 +4134,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -4188,12 +4200,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>163</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -4254,12 +4266,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -4320,12 +4332,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>133.4</t>
+          <t>118.4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>431</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -4378,23 +4390,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>514.9</t>
+          <t>163.1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1812316</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4435,25 +4451,25 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>253.2</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>175</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -4514,12 +4530,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>358.9</t>
+          <t>111.9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>285010</t>
+          <t>288</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -4580,12 +4596,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>262.8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>943</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -4633,25 +4649,25 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>276</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8857.2</t>
+          <t>8663.5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1811922</t>
+          <t>1813591</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -4695,25 +4711,25 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>247</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>276</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>9109.2</t>
+          <t>8660.3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1812065</t>
+          <t>1813496</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -4757,28 +4773,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>271</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>7045.1</t>
+          <t>4701.8</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1812224</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>25280</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4819,28 +4839,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>269</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>5745.4</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1811937</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>37877</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4881,30 +4905,32 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>340</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>6132.3</t>
+          <t>2129.3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1811939</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>6542</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4945,28 +4971,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>10404.2</t>
+          <t>9258.1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1811904</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>75727</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5007,30 +5037,32 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>195</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>8392.6</t>
+          <t>2165.5</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1811824</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>3777</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5071,28 +5103,32 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>253</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>386</v>
+        <v>252</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>10810.9</t>
+          <t>8088.2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1811836</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>46363</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5146,12 +5182,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>9584.9</t>
+          <t>9683.3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>330999</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -5199,30 +5235,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>246</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11933.2</t>
+          <t>3279.4</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1811964</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>5820</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5276,12 +5314,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>12048.6</t>
+          <t>10874</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>359890</t>
+          <t>56901</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -5329,28 +5367,32 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>435</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>436</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>493</v>
+        <v>435</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>17318.4</t>
+          <t>15160.8</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1811813</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>113276</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5367,72 +5409,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -5477,25 +5519,25 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -5556,12 +5598,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -5622,12 +5664,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -5688,12 +5730,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -5754,12 +5796,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>120</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -5820,12 +5862,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>62.1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>125</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -5886,12 +5928,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>333</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -5952,12 +5994,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>118.4</t>
+          <t>133.4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>356</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -6010,27 +6052,23 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>163.1</t>
+          <t>514.9</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1812316</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6071,25 +6109,25 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>253.2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>32216</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -6150,12 +6188,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>358.9</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>285010</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -6216,12 +6254,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>262.8</t>
+          <t>271</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -6269,25 +6307,25 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>8663.5</t>
+          <t>8857.2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1813591</t>
+          <t>1811922</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -6331,25 +6369,25 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>297</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8660.3</t>
+          <t>9109.2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1813496</t>
+          <t>1812065</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -6393,32 +6431,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>268</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>311</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4701.8</t>
+          <t>7045.1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25280</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1812224</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6459,32 +6493,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>312</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>268</v>
+        <v>311</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5745.4</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>37877</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811937</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6525,32 +6555,30 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>340</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2129.3</t>
+          <t>6132.3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6542</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811939</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6591,32 +6619,28 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>327</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>346</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>9258.1</t>
+          <t>10404.2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>75727</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811904</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6657,32 +6681,30 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>195</v>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2165.5</t>
+          <t>8392.6</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3777</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811824</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6723,32 +6745,28 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>331</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>387</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>252</v>
+        <v>386</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8088.2</t>
+          <t>10810.9</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>46363</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811836</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6802,12 +6820,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>9683.3</t>
+          <t>9584.9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>46991</t>
+          <t>330999</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -6855,32 +6873,30 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>246</v>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3279.4</t>
+          <t>11933.2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5820</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811964</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6934,12 +6950,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>12048.6</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>56901</t>
+          <t>359890</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -6987,32 +7003,28 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>424</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>494</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>435</v>
+        <v>493</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>15160.8</t>
+          <t>17318.4</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>113276</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>1811813</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7029,72 +7041,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -8691,72 +8703,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -10353,72 +10365,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Memory limit (MB)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Real time limit (s)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Worker count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Target value</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Lower bound</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Upper bound</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Highest label UNSAT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Lowest label SAT</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Best span</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time consumed (ms)</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
